--- a/data/trans_camb/P1427-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1427-Edad-trans_camb.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -631,14 +631,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>-1,02; 0,0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>-1,03; 0,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,16; 0,0</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,0</t>
+          <t>-0,53; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,69</t>
+          <t>-0,21; 1,61</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>240,46%</t>
+          <t>203,15%</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,17</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,53</t>
+          <t>-0,48; 0,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,0</t>
+          <t>-0,87; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,26</t>
+          <t>-0,16; 0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,05</t>
+          <t>-0,16; 1,21</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>200,3%</t>
+          <t>209,09%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,31</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,15</t>
+          <t>-1,51; -0,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,15</t>
+          <t>-1,51; -0,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,27</t>
+          <t>-0,97; 0,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,66</t>
+          <t>-0,98; 0,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; -0,02</t>
+          <t>-0,95; -0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,13</t>
+          <t>-1,02; 0,03</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>-7,49%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-58,42%</t>
+          <t>-61,98%</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,65</t>
+          <t>-100,0; 99,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,79</t>
+          <t>-100,0; 66,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,4</t>
+          <t>-0,77; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,8</t>
+          <t>-0,84; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,83</t>
+          <t>-0,12; 1,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,01</t>
+          <t>-0,09; 1,33</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121,55%</t>
+          <t>181,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238,1%</t>
+          <t>126,79%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>177,33%</t>
+          <t>150,38%</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,31; —</t>
+          <t>-31,15; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 270,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 958,16</t>
+          <t>-23,46; 1006,59</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,33</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -0,22</t>
+          <t>-3,39; -0,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,7</t>
+          <t>-1,29; 2,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,46</t>
+          <t>-3,03; 1,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,77</t>
+          <t>-2,19; 2,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,11</t>
+          <t>-2,62; 0,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,69</t>
+          <t>-0,99; 1,67</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,75</t>
+          <t>-100,0; 21,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 227,83</t>
+          <t>-38,94; 194,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 82,0</t>
+          <t>-70,53; 78,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 96,42</t>
+          <t>-49,03; 116,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,22; 9,11</t>
+          <t>-73,45; 8,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 92,67</t>
+          <t>-29,45; 94,84</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,74</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,36</t>
+          <t>-7,11; 0,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,61</t>
+          <t>-3,69; 3,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,61</t>
+          <t>-4,9; 2,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 3,85</t>
+          <t>-0,54; 6,21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,43</t>
+          <t>-4,68; 0,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 2,84</t>
+          <t>-1,16; 4,06</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-8,13%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-73,06; 13,69</t>
+          <t>-73,64; 8,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 99,9</t>
+          <t>-37,08; 73,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 51,8</t>
+          <t>-54,3; 50,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 68,74</t>
+          <t>-9,67; 129,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 9,79</t>
+          <t>-53,54; 15,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 44,63</t>
+          <t>-12,78; 77,66</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,63</t>
+          <t>6,1</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 1,24</t>
+          <t>-9,44; 0,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 10,98</t>
+          <t>-0,71; 10,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,7</t>
+          <t>-6,85; 2,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,19</t>
+          <t>2,17; 11,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,69</t>
+          <t>-6,64; 0,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,0</t>
+          <t>2,68; 9,66</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,6; 16,96</t>
+          <t>-63,04; 13,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 144,28</t>
+          <t>-6,35; 123,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 29,17</t>
+          <t>-46,33; 28,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18,64; 113,94</t>
+          <t>11,72; 117,82</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,25; 7,4</t>
+          <t>-47,43; 2,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,25; 99,78</t>
+          <t>17,08; 96,32</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,35</t>
+          <t>-1,58; -0,33</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,83</t>
+          <t>0,35; 1,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,37</t>
+          <t>-1,09; 0,38</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,45</t>
+          <t>1,06; 2,5</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,14</t>
+          <t>-1,09; -0,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,92</t>
+          <t>0,9; 1,96</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-65,59; -20,24</t>
+          <t>-65,58; -19,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5,28; 111,94</t>
+          <t>14,11; 116,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 15,16</t>
+          <t>-36,48; 18,73</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16,11; 109,35</t>
+          <t>33,82; 114,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-45,07; -6,62</t>
+          <t>-42,86; -6,16</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,34; 93,02</t>
+          <t>35,26; 96,14</t>
         </is>
       </c>
     </row>
